--- a/data/trans_camb/P1001-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1001-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,08</t>
+          <t>-0,82; 5,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 0,76</t>
+          <t>-4,54; 1,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 3,81</t>
+          <t>-2,47; 3,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 13,45</t>
+          <t>7,18; 13,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 12,37</t>
+          <t>5,87; 12,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,54; 12,66</t>
+          <t>6,42; 12,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,3</t>
+          <t>4,98; 9,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,72</t>
+          <t>1,98; 6,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 8,4</t>
+          <t>3,88; 8,58</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 50,14</t>
+          <t>-6,35; 55,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,05; 7,61</t>
+          <t>-38,21; 12,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 39,98</t>
+          <t>-20,06; 38,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,02; 109,33</t>
+          <t>48,38; 107,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,03; 99,95</t>
+          <t>39,01; 100,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,86; 101,58</t>
+          <t>41,59; 102,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,81; 80,61</t>
+          <t>36,55; 78,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,47; 57,67</t>
+          <t>14,33; 55,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,28; 73,21</t>
+          <t>28,7; 74,16</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,53</t>
+          <t>-0,32; 2,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,68</t>
+          <t>0,78; 3,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,87</t>
+          <t>-0,5; 2,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,83</t>
+          <t>1,08; 4,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,55</t>
+          <t>-0,28; 3,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,53</t>
+          <t>-1,55; 2,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,14</t>
+          <t>0,68; 3,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,1</t>
+          <t>0,72; 3,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,18</t>
+          <t>-0,4; 2,37</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 91,68</t>
+          <t>-9,14; 75,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,84; 129,78</t>
+          <t>17,62; 120,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 96,8</t>
+          <t>-12,07; 96,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,72; 78,35</t>
+          <t>13,22; 79,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 58,69</t>
+          <t>-3,07; 59,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 41,08</t>
+          <t>-19,61; 42,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,01; 66,45</t>
+          <t>10,38; 63,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,64; 67,56</t>
+          <t>13,07; 63,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 44,89</t>
+          <t>-6,95; 49,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 3,89</t>
+          <t>-2,42; 3,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,22</t>
+          <t>-3,43; 1,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 2,32</t>
+          <t>-2,28; 2,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 2,43</t>
+          <t>-3,57; 2,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 3,23</t>
+          <t>-2,28; 3,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,3</t>
+          <t>-1,34; 4,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,26</t>
+          <t>-1,91; 2,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,49</t>
+          <t>-2,15; 1,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,74</t>
+          <t>-1,09; 2,6</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 132,37</t>
+          <t>-45,63; 128,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,07; 47,38</t>
+          <t>-65,29; 50,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 81,03</t>
+          <t>-44,27; 83,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,75; 56,05</t>
+          <t>-49,4; 61,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,22; 72,82</t>
+          <t>-31,79; 80,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 108,66</t>
+          <t>-19,65; 99,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 60,61</t>
+          <t>-33,38; 58,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 41,78</t>
+          <t>-37,59; 39,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 70,74</t>
+          <t>-17,36; 67,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,38</t>
+          <t>-0,19; 2,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,24</t>
+          <t>-1,06; 1,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,01</t>
+          <t>-1,87; 1,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,64; 6,67</t>
+          <t>3,68; 7,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,33</t>
+          <t>1,3; 4,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,02</t>
+          <t>-0,75; 2,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,15</t>
+          <t>2,11; 4,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,48</t>
+          <t>0,55; 2,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,65</t>
+          <t>-0,71; 1,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 44,47</t>
+          <t>-2,99; 40,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 22,93</t>
+          <t>-16,45; 23,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 17,85</t>
+          <t>-28,19; 18,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,62; 76,28</t>
+          <t>36,46; 80,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,13; 49,76</t>
+          <t>12,85; 50,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 33,91</t>
+          <t>-7,28; 34,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,52; 57,53</t>
+          <t>25,0; 57,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,94; 33,87</t>
+          <t>6,46; 34,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 22,47</t>
+          <t>-8,87; 23,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1001-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1001-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,53</t>
+          <t>9,11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,97</t>
+          <t>5,42</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 5,29</t>
+          <t>-0,82; 5,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 1,23</t>
+          <t>-4,72; 1,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 3,91</t>
+          <t>-3,0; 3,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 13,35</t>
+          <t>7,53; 13,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,87; 12,33</t>
+          <t>5,81; 12,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 12,61</t>
+          <t>6,33; 12,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,07</t>
+          <t>4,78; 9,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,45</t>
+          <t>2,15; 6,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,58</t>
+          <t>3,43; 7,68</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 55,28</t>
+          <t>-6,94; 56,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,21; 12,57</t>
+          <t>-37,79; 12,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,06; 38,8</t>
+          <t>-24,06; 31,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,38; 107,62</t>
+          <t>49,2; 107,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,01; 100,18</t>
+          <t>38,11; 98,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,59; 102,86</t>
+          <t>41,61; 99,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,55; 78,9</t>
+          <t>35,18; 77,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,33; 55,35</t>
+          <t>15,76; 58,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,7; 74,16</t>
+          <t>25,66; 65,37</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>1,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,38</t>
+          <t>-0,38; 2,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,52</t>
+          <t>0,8; 3,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 2,97</t>
+          <t>0,45; 3,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,93</t>
+          <t>0,83; 4,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,53</t>
+          <t>-0,26; 3,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,6</t>
+          <t>0,09; 3,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,01</t>
+          <t>0,68; 2,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,0</t>
+          <t>0,82; 3,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,37</t>
+          <t>0,8; 2,95</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>48,76%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41,76%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,54%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>35,96%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41,76%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,96%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>37,61%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 75,47</t>
+          <t>-9,41; 80,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,62; 120,33</t>
+          <t>15,46; 117,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 96,97</t>
+          <t>10,5; 111,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,22; 79,44</t>
+          <t>10,43; 78,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 59,36</t>
+          <t>-3,47; 57,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 42,93</t>
+          <t>0,86; 57,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 63,23</t>
+          <t>10,99; 63,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,07; 63,88</t>
+          <t>13,34; 66,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 49,87</t>
+          <t>13,82; 64,87</t>
         </is>
       </c>
     </row>
@@ -1066,29 +1066,29 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>-0,03</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>-0,63</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,33</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>0,04</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>-0,32</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>1,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,65</t>
+          <t>-2,14; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,26</t>
+          <t>-3,79; 1,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 2,27</t>
+          <t>-2,47; 2,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 2,52</t>
+          <t>-3,35; 2,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,45</t>
+          <t>-2,68; 3,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,15</t>
+          <t>-0,86; 4,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,29</t>
+          <t>-1,95; 2,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,56</t>
+          <t>-2,33; 1,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,6</t>
+          <t>-0,88; 2,87</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>-0,67%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,63; 128,26</t>
+          <t>-43,6; 122,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-65,29; 50,7</t>
+          <t>-64,12; 53,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,27; 83,96</t>
+          <t>-46,13; 80,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,4; 61,18</t>
+          <t>-47,91; 68,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 80,86</t>
+          <t>-37,24; 78,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 99,59</t>
+          <t>-13,42; 110,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,38; 58,54</t>
+          <t>-35,57; 60,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,59; 39,75</t>
+          <t>-40,82; 39,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 67,2</t>
+          <t>-13,92; 76,02</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>1,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,26</t>
+          <t>-0,2; 2,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,35</t>
+          <t>-1,04; 1,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,03</t>
+          <t>-1,27; 1,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,01</t>
+          <t>3,63; 6,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,39</t>
+          <t>1,24; 4,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,98</t>
+          <t>1,0; 3,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,16</t>
+          <t>2,02; 4,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,53</t>
+          <t>0,54; 2,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,71</t>
+          <t>0,3; 2,13</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-5,02%</t>
+          <t>-0,33%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 40,92</t>
+          <t>-3,45; 41,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 23,93</t>
+          <t>-15,86; 23,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,19; 18,38</t>
+          <t>-19,48; 20,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36,46; 80,51</t>
+          <t>34,79; 76,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,85; 50,66</t>
+          <t>12,02; 48,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 34,55</t>
+          <t>9,24; 41,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,0; 57,06</t>
+          <t>25,09; 56,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,46; 34,56</t>
+          <t>6,68; 33,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 23,02</t>
+          <t>3,18; 29,66</t>
         </is>
       </c>
     </row>
